--- a/stikerts/Testing/Test-Tracking-Sheet.xlsx
+++ b/stikerts/Testing/Test-Tracking-Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liron\Local Sites\ordermachine\app\public\wp-content\plugins\orderMachine\stikerts\Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5976722E-82AC-41EC-9557-F75FAE0C3474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{401DF3FC-2A40-4003-8DE4-FA9A8F99799E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Read Me" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="180">
   <si>
     <t>Bin Sticker — Test Tracking Workbook</t>
   </si>
@@ -564,6 +564,24 @@
   </si>
   <si>
     <t>Fail</t>
+  </si>
+  <si>
+    <t>number 2</t>
+  </si>
+  <si>
+    <t>Marginal</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>number 1]</t>
+  </si>
+  <si>
+    <t>numbrt 6</t>
   </si>
 </sst>
 </file>
@@ -1214,10 +1232,18 @@
       <c r="A12" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
+      <c r="B12" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="F12" s="2" t="s">
         <v>167</v>
       </c>
@@ -1226,10 +1252,18 @@
       <c r="A13" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
+      <c r="B13" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>173</v>
+      </c>
       <c r="F13" s="2" t="s">
         <v>165</v>
       </c>
@@ -1477,7 +1511,9 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
-      <c r="F35" s="2"/>
+      <c r="F35" s="2" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
@@ -1487,7 +1523,9 @@
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
-      <c r="F36" s="2"/>
+      <c r="F36" s="2" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
@@ -1518,21 +1556,41 @@
       <c r="A40" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="2"/>
+      <c r="B40" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="2"/>
+      <c r="B41" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
@@ -1577,7 +1635,9 @@
       <c r="A48" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B48" s="3"/>
+      <c r="B48" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
       <c r="E48" s="9"/>
@@ -1587,7 +1647,9 @@
       <c r="A49" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B49" s="3"/>
+      <c r="B49" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
@@ -1597,7 +1659,9 @@
       <c r="A50" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B50" s="3"/>
+      <c r="B50" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
@@ -2556,7 +2620,9 @@
       <c r="C7" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="D7" s="3"/>
+      <c r="D7" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="E7" s="3"/>
       <c r="F7" s="2"/>
     </row>
@@ -2566,7 +2632,9 @@
       <c r="C8" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="D8" s="3"/>
+      <c r="D8" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="E8" s="3"/>
       <c r="F8" s="2"/>
     </row>
@@ -2576,7 +2644,9 @@
       <c r="C9" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="D9" s="3"/>
+      <c r="D9" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="E9" s="3"/>
       <c r="F9" s="2"/>
     </row>
@@ -2590,7 +2660,9 @@
       <c r="C10" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="D10" s="3"/>
+      <c r="D10" s="3" t="s">
+        <v>173</v>
+      </c>
       <c r="E10" s="3"/>
       <c r="F10" s="2"/>
     </row>
@@ -2600,7 +2672,9 @@
       <c r="C11" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="D11" s="3"/>
+      <c r="D11" s="3" t="s">
+        <v>173</v>
+      </c>
       <c r="E11" s="3"/>
       <c r="F11" s="2"/>
     </row>
@@ -2610,7 +2684,9 @@
       <c r="C12" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="D12" s="3"/>
+      <c r="D12" s="3" t="s">
+        <v>173</v>
+      </c>
       <c r="E12" s="3"/>
       <c r="F12" s="2"/>
     </row>
@@ -2624,7 +2700,9 @@
       <c r="C13" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="D13" s="3"/>
+      <c r="D13" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="E13" s="3"/>
       <c r="F13" s="2"/>
     </row>
@@ -2634,7 +2712,9 @@
       <c r="C14" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="D14" s="3"/>
+      <c r="D14" s="3" t="s">
+        <v>175</v>
+      </c>
       <c r="E14" s="3"/>
       <c r="F14" s="2"/>
     </row>
@@ -2644,7 +2724,9 @@
       <c r="C15" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="D15" s="3"/>
+      <c r="D15" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="E15" s="3"/>
       <c r="F15" s="2"/>
     </row>
@@ -2658,7 +2740,9 @@
       <c r="C16" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="D16" s="3"/>
+      <c r="D16" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="E16" s="3"/>
       <c r="F16" s="2"/>
     </row>
@@ -2668,7 +2752,9 @@
       <c r="C17" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="D17" s="3"/>
+      <c r="D17" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="E17" s="3"/>
       <c r="F17" s="2"/>
     </row>
@@ -2678,7 +2764,9 @@
       <c r="C18" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="D18" s="3"/>
+      <c r="D18" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="E18" s="3"/>
       <c r="F18" s="2"/>
     </row>
@@ -2692,8 +2780,12 @@
       <c r="C19" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
+      <c r="D19" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>176</v>
+      </c>
       <c r="F19" s="2"/>
     </row>
     <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2702,8 +2794,12 @@
       <c r="C20" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
+      <c r="D20" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>176</v>
+      </c>
       <c r="F20" s="2"/>
     </row>
     <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2712,8 +2808,12 @@
       <c r="C21" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
+      <c r="D21" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>176</v>
+      </c>
       <c r="F21" s="2"/>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">

--- a/stikerts/Testing/Test-Tracking-Sheet.xlsx
+++ b/stikerts/Testing/Test-Tracking-Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liron\Local Sites\ordermachine\app\public\wp-content\plugins\orderMachine\stikerts\Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{401DF3FC-2A40-4003-8DE4-FA9A8F99799E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB4A38A-2D7E-452F-A15C-CF957B8012EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="181">
   <si>
     <t>Bin Sticker — Test Tracking Workbook</t>
   </si>
@@ -582,6 +582,9 @@
   </si>
   <si>
     <t>numbrt 6</t>
+  </si>
+  <si>
+    <t>not really</t>
   </si>
 </sst>
 </file>
@@ -751,10 +754,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -1507,10 +1510,18 @@
       <c r="A35" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
+      <c r="B35" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="F35" s="2" t="s">
         <v>174</v>
       </c>
@@ -1519,10 +1530,18 @@
       <c r="A36" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
+      <c r="B36" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="F36" s="2" t="s">
         <v>174</v>
       </c>
@@ -1615,7 +1634,9 @@
       <c r="A46" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B46" s="3"/>
+      <c r="B46" s="3" t="s">
+        <v>180</v>
+      </c>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
@@ -1625,7 +1646,9 @@
       <c r="A47" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B47" s="3"/>
+      <c r="B47" s="3" t="s">
+        <v>180</v>
+      </c>
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
@@ -2194,15 +2217,15 @@
       <c r="G37" s="3"/>
     </row>
     <row r="39" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="15" t="s">
+      <c r="A39" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="B39" s="15"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
+      <c r="B39" s="16"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
     </row>
     <row r="40" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
@@ -2226,11 +2249,11 @@
       <c r="B41" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="16"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="15"/>
     </row>
     <row r="42" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
@@ -2239,11 +2262,11 @@
       <c r="B42" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
     </row>
     <row r="43" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
@@ -2252,11 +2275,11 @@
       <c r="B43" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C43" s="16"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="16"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="15"/>
     </row>
     <row r="44" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
@@ -2265,11 +2288,11 @@
       <c r="B44" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C44" s="16"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="16"/>
-      <c r="G44" s="16"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="15"/>
     </row>
     <row r="45" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
@@ -2278,11 +2301,11 @@
       <c r="B45" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C45" s="16"/>
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
-      <c r="F45" s="16"/>
-      <c r="G45" s="16"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="15"/>
     </row>
     <row r="46" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
@@ -2291,11 +2314,11 @@
       <c r="B46" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="16"/>
-      <c r="E46" s="16"/>
-      <c r="F46" s="16"/>
-      <c r="G46" s="16"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="15"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="15"/>
     </row>
     <row r="47" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
@@ -2304,11 +2327,11 @@
       <c r="B47" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C47" s="16"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="16"/>
-      <c r="G47" s="16"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="15"/>
     </row>
     <row r="48" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
@@ -2317,11 +2340,11 @@
       <c r="B48" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C48" s="16"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="16"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="15"/>
     </row>
     <row r="50" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
@@ -2347,6 +2370,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
     <mergeCell ref="C48:G48"/>
     <mergeCell ref="A52:G52"/>
     <mergeCell ref="C43:G43"/>
@@ -2354,11 +2382,6 @@
     <mergeCell ref="C45:G45"/>
     <mergeCell ref="C46:G46"/>
     <mergeCell ref="C47:G47"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" sqref="C19:F26" xr:uid="{00000000-0002-0000-0200-000000000000}">
